--- a/news_daily/2026-08-29.xlsx
+++ b/news_daily/2026-08-29.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1169,6 +1197,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1339,6 +1371,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1389,13 +1425,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1444,7 +1484,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>58a4ed0bd40b433fbc88436d96d7602f</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>3690d963339cc65abc8f07c9</t>
@@ -1465,7 +1509,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -1509,6 +1557,18 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1679,6 +1739,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1841,6 +1905,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2011,6 +2079,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2181,6 +2253,10 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2351,318 +2427,362 @@
       </c>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2026-08-29T08:00:28+08:00</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2640082</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>393f65ea16664580833374e69fed37da</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>9803e8a4715924fd06a8fa3c</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>d6721a5147e05e76cff03436</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr"/>
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>公司名稱／股票代號歧義</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>d6721a5147e05e76cff03436</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr"/>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr"/>
+      <c r="BF11" s="3" t="inlineStr"/>
+      <c r="BG11" s="3" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2026-08-29T08:00:28+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2640082</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>a9d39c8473e842c3bd00dc7e0f804f0e</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>9803e8a4715924fd06a8fa3c</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>279b5b5b42a43fe1539f14f0</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr"/>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>279b5b5b42a43fe1539f14f0</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr">
         <is>
           <t>GOOG</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE12" s="4" t="inlineStr"/>
-      <c r="BF12" s="4" t="inlineStr"/>
-      <c r="BG12" s="4" t="inlineStr"/>
-      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr"/>
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2833,6 +2953,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3003,6 +3127,10 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3173,168 +3301,200 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>DTE</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>DTE Energy</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>2026-08-29T03:39:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Attorney General Dana Nessel seeks deep cuts to DTE’s $474 million rate request</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>'-0.807</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTlYyS3BtUXprYnA2SHVkREJoSW5EUmV2UjdFLWtfY0lReW9mNnFfdHV6d3dEaENwUEdTZnFTenJWNklfMjdjaTRQRDl0RzB2SFEwMVdzNXhfeERHSDQ1dTJTVzZKdmlvcl80aDlPYTZfbnA1aWlRWnRzaXUwTmk5bUNZT3hYT1ZnaUVNcllVR3pSSllGdldUWnRoT0FWZzc3OHhDMVBVa1JjU28?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>WILX</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>5f1a4d8395384a0ba1ecf919854bb39a</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>8a5f31a9d2d9790812a9b6cb</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>ca55499683ca7bec961b27bb</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>'-0.807</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTlYyS3BtUXprYnA2SHVkREJoSW5EUmV2UjdFLWtfY0lReW9mNnFfdHV6d3dEaENwUEdTZnFTenJWNklfMjdjaTRQRDl0RzB2SFEwMVdzNXhfeERHSDQ1dTJTVzZKdmlvcl80aDlPYTZfbnA1aWlRWnRzaXUwTmk5bUNZT3hYT1ZnaUVNcllVR3pSSllGdldUWnRoT0FWZzc3OHhDMVBVa1JjU28?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>WILX</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>8a5f31a9d2d9790812a9b6cb</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>ca55499683ca7bec961b27bb</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr"/>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr"/>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
         <is>
           <t>DTE</t>
         </is>
       </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF16" s="4" t="inlineStr"/>
-      <c r="BG16" s="4" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3505,6 +3665,10 @@
       </c>
       <c r="BG17" s="3" t="inlineStr"/>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr"/>
+      <c r="BL17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3555,13 +3719,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -3610,7 +3778,11 @@
         </is>
       </c>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>682efa9e1e934abcbfc26cf64682625c</t>
+        </is>
+      </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>85b1ba799ab341a48dcf815b</t>
@@ -3631,7 +3803,11 @@
       <c r="AL18" s="4" t="inlineStr"/>
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="4" t="inlineStr"/>
       <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
@@ -3667,9 +3843,21 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH18"/>
+  <autoFilter ref="A1:BL18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3680,7 +3868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3743,6 +3931,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4044,6 +4236,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4216,6 +4428,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4266,13 +4482,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -4321,7 +4541,11 @@
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>58a4ed0bd40b433fbc88436d96d7602f</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>3690d963339cc65abc8f07c9</t>
@@ -4342,7 +4566,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -4386,6 +4614,18 @@
         </is>
       </c>
       <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4398,20 +4638,24 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T08:00:28+08:00</t>
+          <t>2026-08-29T00:15:00+08:00</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
+          <t>Pentair plc (PNR) Investors: Securities Fraud Class Action Filed, Contact Hagens Berman Before October 2, 2026 Lead Plaintiff Deadline</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -4432,17 +4676,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -4450,24 +4694,28 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.122</t>
+        </is>
+      </c>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>公司名稱／股票代號歧義</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOTlgyUnVFakdSSGI2RTlJTjg0X20wWmZ0WGZsaDh1UFJzTlJZZ3F2UEpBcFZFaVA5bGhEQTJfb3RJRmltMVBaOHNYNEdaSFd1NFNET2p4UENMTjJxWmdFM082Vnh3YnJSWi1VYWZRejhCY0FUMm4ybjQyNjJJbU1GQlJFMUNJLTYwaWp2a29MSG9KUUw2WWpiYVR3Qk1GLTRLbVp3Tnd6TF9TQXlyZHVMU3JnaUtsSm5sdjJnejcyajZCUUFqSTF4VHFsS2pkTWlHeW5rRXlpX09JdERHTFdEb2oxTzd1bXNuVFpzVDFZeTBNeWhqUXZwMFN1ekhYMGJlcXk4Ny1Kd0xNVjdfM08wRkV6RQ?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
@@ -4483,19 +4731,23 @@
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>訴訟</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>682efa9e1e934abcbfc26cf64682625c</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
+          <t>85b1ba799ab341a48dcf815b</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>d6721a5147e05e76cff03436</t>
+          <t>f94f68e6c30c6b9ec890c074</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr"/>
@@ -4510,7 +4762,7 @@
       <c r="AN4" s="4" t="inlineStr"/>
       <c r="AO4" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP4" s="4" t="inlineStr"/>
@@ -4527,504 +4779,42 @@
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
         <is>
-          <t>公司名稱／股票代號歧義</t>
+          <t>已核對</t>
         </is>
       </c>
       <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
       <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr"/>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
       <c r="BH4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class C)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29T08:00:28+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>279b5b5b42a43fe1539f14f0</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE5" s="4" t="inlineStr"/>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>DTE</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>DTE Energy</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29T03:39:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Attorney General Dana Nessel seeks deep cuts to DTE’s $474 million rate request</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>'-0.807</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTlYyS3BtUXprYnA2SHVkREJoSW5EUmV2UjdFLWtfY0lReW9mNnFfdHV6d3dEaENwUEdTZnFTenJWNklfMjdjaTRQRDl0RzB2SFEwMVdzNXhfeERHSDQ1dTJTVzZKdmlvcl80aDlPYTZfbnA1aWlRWnRzaXUwTmk5bUNZT3hYT1ZnaUVNcllVR3pSSllGdldUWnRoT0FWZzc3OHhDMVBVa1JjU28?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>WILX</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>8a5f31a9d2d9790812a9b6cb</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>ca55499683ca7bec961b27bb</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>DTE</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29T00:15:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pentair plc (PNR) Investors: Securities Fraud Class Action Filed, Contact Hagens Berman Before October 2, 2026 Lead Plaintiff Deadline</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.122</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOTlgyUnVFakdSSGI2RTlJTjg0X20wWmZ0WGZsaDh1UFJzTlJZZ3F2UEpBcFZFaVA5bGhEQTJfb3RJRmltMVBaOHNYNEdaSFd1NFNET2p4UENMTjJxWmdFM082Vnh3YnJSWi1VYWZRejhCY0FUMm4ybjQyNjJJbU1GQlJFMUNJLTYwaWp2a29MSG9KUUw2WWpiYVR3Qk1GLTRLbVp3Tnd6TF9TQXlyZHVMU3JnaUtsSm5sdjJnejcyajZCUUFqSTF4VHFsS2pkTWlHeW5rRXlpX09JdERHTFdEb2oxTzd1bXNuVFpzVDFZeTBNeWhqUXZwMFN1ekhYMGJlcXk4Ny1Kd0xNVjdfM08wRkV6RQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>85b1ba799ab341a48dcf815b</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>f94f68e6c30c6b9ec890c074</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5035,7 +4825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5098,6 +4888,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5399,6 +5193,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -5571,491 +5385,187 @@
       </c>
       <c r="BG2" s="3" t="inlineStr"/>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class A)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29T08:00:28+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:12:26+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Oglethorpe business dean: The real challenge isn’t tariffs. It’s uncertainty.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>關稅</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>d6721a5147e05e76cff03436</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.056</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbTVfWTlmaXVNOGJJang2T0JzRWU1bTNUenNhQy1Qc1pQVEt6dmhGYUM1ei1HWWh4U1pVTG94dGo4dzFNbHJXY2NhRXVoN2ZLU0pWemowazRVbDBxZFJ3TUJnQUR0UGJTOVl4Y2RKUE9vc1RMZTVFdWszOEJCU2x5MXB6Q2dIcnBhNEw4MFI1WVFOaHhzSV80OXNaR1J6OG1PSmJN?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Oglethorpe University</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>9a79d41fb765245cc949ebda</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>424ec9fe8cf8b9b4b05a5c65</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr"/>
-      <c r="BF3" s="4" t="inlineStr"/>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class C)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29T08:00:28+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>谷歌隱私訴訟案產生高達1.47億美元律師費</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640082</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>9803e8a4715924fd06a8fa3c</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>279b5b5b42a43fe1539f14f0</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr"/>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29T02:12:26+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Oglethorpe business dean: The real challenge isn’t tariffs. It’s uncertainty.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.056</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbTVfWTlmaXVNOGJJang2T0JzRWU1bTNUenNhQy1Qc1pQVEt6dmhGYUM1ei1HWWh4U1pVTG94dGo4dzFNbHJXY2NhRXVoN2ZLU0pWemowazRVbDBxZFJ3TUJnQUR0UGJTOVl4Y2RKUE9vc1RMZTVFdWszOEJCU2x5MXB6Q2dIcnBhNEw4MFI1WVFOaHhzSV80OXNaR1J6OG1PSmJN?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Oglethorpe University</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>tariff</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>9a79d41fb765245cc949ebda</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>424ec9fe8cf8b9b4b05a5c65</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6066,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6129,6 +5639,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6432,9 +5946,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6445,7 +5979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6495,134 +6029,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6632,46 +6166,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -6680,12 +6248,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6695,90 +6263,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6788,94 +6360,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6883,89 +6455,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-29.xlsx
+++ b/news_daily/2026-08-29.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>376bfaa9c2544b8a9ffa85cea8534635</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>73d1e7e51675430a12ad0018</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1025,8 +1037,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2288,32 +2308,32 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2353,7 +2373,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -2362,7 +2382,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>0e033721e99d403d9076ac1516d19e03</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>ef4f6b78953ec55dbcedda38</t>
@@ -2385,7 +2409,7 @@
       <c r="AN10" s="3" t="inlineStr"/>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr"/>
@@ -2427,10 +2451,22 @@
       </c>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3526,32 +3562,32 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3591,7 +3627,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -3600,7 +3636,11 @@
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>b26314024ee94927a14eb797a7d0c428</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>9a79d41fb765245cc949ebda</t>
@@ -3623,7 +3663,7 @@
       <c r="AN17" s="3" t="inlineStr"/>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr"/>
@@ -3665,10 +3705,22 @@
       </c>
       <c r="BG17" s="3" t="inlineStr"/>
       <c r="BH17" s="3" t="inlineStr"/>
-      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="3" t="inlineStr"/>
-      <c r="BK17" s="3" t="inlineStr"/>
-      <c r="BL17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4308,13 +4360,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -4363,7 +4419,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>376bfaa9c2544b8a9ffa85cea8534635</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>73d1e7e51675430a12ad0018</t>
@@ -4384,7 +4444,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -4430,8 +4494,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4825,7 +4897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL3"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5216,356 +5288,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>AppLovin</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29T08:02:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Researchers at USF St. Pete develop flood tracking app</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQd1FvZGNOTk5tUkFpdjRuWXFKS1lLZG56aTV3VXFzZUtDMlp1blg1X3RaVHdmNXk4akF4VHFTT1BSUTVwaDEzMktOalFpUmJ5RF80OWF4RWFCeEQ5SER6ODNseEw1TkJNeEFpOWpCMHNwWGVJdVloTjdGaG5TUXdUMTVBbWUtdVZrTzd3OVFRZ2xsZkRrWHlTVXdEVjA?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>wtsp.com</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>ef4f6b78953ec55dbcedda38</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>c43c71c15a905db520665db4</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29T02:12:26+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Oglethorpe business dean: The real challenge isn’t tariffs. It’s uncertainty.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.056</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbTVfWTlmaXVNOGJJang2T0JzRWU1bTNUenNhQy1Qc1pQVEt6dmhGYUM1ei1HWWh4U1pVTG94dGo4dzFNbHJXY2NhRXVoN2ZLU0pWemowazRVbDBxZFJ3TUJnQUR0UGJTOVl4Y2RKUE9vc1RMZTVFdWszOEJCU2x5MXB6Q2dIcnBhNEw4MFI1WVFOaHhzSV80OXNaR1J6OG1PSmJN?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Oglethorpe University</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>tariff</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>9a79d41fb765245cc949ebda</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>424ec9fe8cf8b9b4b05a5c65</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL3"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-29.xlsx
+++ b/news_daily/2026-08-29.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -1082,28 +1082,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1143,7 +1147,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1152,7 +1156,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>69cd1522ecc34556b6b8b654ac984d74</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>b5007c1c55ca7103d239ce5c</t>
@@ -1173,7 +1181,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1217,10 +1229,22 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1256,28 +1280,32 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1317,7 +1345,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1326,7 +1354,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>adbd8ad5129f423fa36ebfcc5cd54d6f</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>16163f636d7c06c04fc4155b</t>
@@ -1347,7 +1379,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1391,10 +1427,22 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1639,13 +1687,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1694,7 +1746,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>3901f329e4dd4e4b9f63e2967ce9ef62</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>f35576a277671137428544a5</t>
@@ -1715,7 +1771,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1761,174 +1821,206 @@
       <c r="BH6" s="3" t="inlineStr"/>
       <c r="BI6" s="3" t="inlineStr"/>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Weyerhaeuser</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-08-29T09:30:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Weyerhaeuser sued over Lincoln County landslide that buried Highway 229</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.865</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNR3ROYnZQWkpJb28xeFA3aDgwcXN5V2tLcFo2SGIwUnpzNGtpMk9HSF80UzhsWm9xVmFzUWpDcWVTUExPYmFPMW43VE9SaGpILW5wQ2FtbFFGT0ZmdzB3bU1pTkQ2QnFuWHZ6aWFDVWlVX3RLNFVYSk1BV3BQQWtvTEVReHdPVlFTb3lSQW5uMDJsY3ZwQVhRSW5HTGI4bVY5dmFLakYyZ0NQOF9tX1ZBUW1Ta1kxMXNPblNoQ0N3elozY2tDRDFDeEtrdHJaeTh1ZUczanVwVHRvcDFuSlVlMmxEd0pGRDBRX2FLeg?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Central Oregon Daily</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>a563aa0dee7745368648125df03f83c6</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>9e104bf48496358f50f2b108</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>89605e094136989845ddc0b1</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.865</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNR3ROYnZQWkpJb28xeFA3aDgwcXN5V2tLcFo2SGIwUnpzNGtpMk9HSF80UzhsWm9xVmFzUWpDcWVTUExPYmFPMW43VE9SaGpILW5wQ2FtbFFGT0ZmdzB3bU1pTkQ2QnFuWHZ6aWFDVWlVX3RLNFVYSk1BV3BQQWtvTEVReHdPVlFTb3lSQW5uMDJsY3ZwQVhRSW5HTGI4bVY5dmFLakYyZ0NQOF9tX1ZBUW1Ta1kxMXNPblNoQ0N3elozY2tDRDFDeEtrdHJaeTh1ZUczanVwVHRvcDFuSlVlMmxEd0pGRDBRX2FLeg?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Central Oregon Daily</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>landslide</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>9e104bf48496358f50f2b108</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>89605e094136989845ddc0b1</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1964,28 +2056,32 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -2025,7 +2121,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -2034,7 +2130,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>b0de7276779f4db48119393d23ca87f5</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>92e7f656451f74887d6c0713</t>
@@ -2055,7 +2155,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2099,10 +2203,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2138,28 +2254,32 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2199,7 +2319,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -2208,7 +2328,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>617bf4f27d104da68172a9b3c4da339f</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>877b7239a02230817adc7367</t>
@@ -2229,7 +2353,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2273,10 +2401,22 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2854,28 +2994,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2915,7 +3059,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2924,7 +3068,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>ee717cce16844816ae511306d4073b40</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>38a2cff944380bde0e9ca40c</t>
@@ -2945,7 +3093,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2989,10 +3141,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3028,28 +3192,32 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3089,7 +3257,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -3098,7 +3266,11 @@
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>34c6caa3412a45b7a2a2f3143b5d7833</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>a6fa0b0e4f408a671c81c7db</t>
@@ -3119,7 +3291,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3163,10 +3339,22 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3202,28 +3390,32 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3263,7 +3455,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -3272,7 +3464,11 @@
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>df617190c7604b879a00a66783bfd5a4</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>2e5dd3a333d22fae006c0698</t>
@@ -3293,7 +3489,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -3337,10 +3537,22 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3920,7 +4132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL4"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4712,22 +4924,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T00:15:00+08:00</t>
+          <t>2026-08-29T09:30:00+08:00</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Pentair plc (PNR) Investors: Securities Fraud Class Action Filed, Contact Hagens Berman Before October 2, 2026 Lead Plaintiff Deadline</t>
+          <t>Weyerhaeuser sued over Lincoln County landslide that buried Highway 229</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -4768,7 +4980,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>'-0.122</t>
+          <t>'-0.865</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -4782,18 +4994,18 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOTlgyUnVFakdSSGI2RTlJTjg0X20wWmZ0WGZsaDh1UFJzTlJZZ3F2UEpBcFZFaVA5bGhEQTJfb3RJRmltMVBaOHNYNEdaSFd1NFNET2p4UENMTjJxWmdFM082Vnh3YnJSWi1VYWZRejhCY0FUMm4ybjQyNjJJbU1GQlJFMUNJLTYwaWp2a29MSG9KUUw2WWpiYVR3Qk1GLTRLbVp3Tnd6TF9TQXlyZHVMU3JnaUtsSm5sdjJnejcyajZCUUFqSTF4VHFsS2pkTWlHeW5rRXlpX09JdERHTFdEb2oxTzd1bXNuVFpzVDFZeTBNeWhqUXZwMFN1ekhYMGJlcXk4Ny1Kd0xNVjdfM08wRkV6RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNR3ROYnZQWkpJb28xeFA3aDgwcXN5V2tLcFo2SGIwUnpzNGtpMk9HSF80UzhsWm9xVmFzUWpDcWVTUExPYmFPMW43VE9SaGpILW5wQ2FtbFFGT0ZmdzB3bU1pTkQ2QnFuWHZ6aWFDVWlVX3RLNFVYSk1BV3BQQWtvTEVReHdPVlFTb3lSQW5uMDJsY3ZwQVhRSW5HTGI4bVY5dmFLakYyZ0NQOF9tX1ZBUW1Ta1kxMXNPblNoQ0N3elozY2tDRDFDeEtrdHJaeTh1ZUczanVwVHRvcDFuSlVlMmxEd0pGRDBRX2FLeg?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>Central Oregon Daily</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y4" s="4" t="inlineStr">
@@ -4803,23 +5015,23 @@
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>landslide</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>682efa9e1e934abcbfc26cf64682625c</t>
+          <t>a563aa0dee7745368648125df03f83c6</t>
         </is>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>85b1ba799ab341a48dcf815b</t>
+          <t>9e104bf48496358f50f2b108</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>f94f68e6c30c6b9ec890c074</t>
+          <t>89605e094136989845ddc0b1</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr"/>
@@ -4851,7 +5063,7 @@
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -4872,7 +5084,11 @@
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="4" t="inlineStr"/>
       <c r="BK4" s="4" t="inlineStr">
         <is>
@@ -4881,12 +5097,198 @@
       </c>
       <c r="BL4" s="4" t="inlineStr">
         <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T00:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Pentair plc (PNR) Investors: Securities Fraud Class Action Filed, Contact Hagens Berman Before October 2, 2026 Lead Plaintiff Deadline</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.122</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOTlgyUnVFakdSSGI2RTlJTjg0X20wWmZ0WGZsaDh1UFJzTlJZZ3F2UEpBcFZFaVA5bGhEQTJfb3RJRmltMVBaOHNYNEdaSFd1NFNET2p4UENMTjJxWmdFM082Vnh3YnJSWi1VYWZRejhCY0FUMm4ybjQyNjJJbU1GQlJFMUNJLTYwaWp2a29MSG9KUUw2WWpiYVR3Qk1GLTRLbVp3Tnd6TF9TQXlyZHVMU3JnaUtsSm5sdjJnejcyajZCUUFqSTF4VHFsS2pkTWlHeW5rRXlpX09JdERHTFdEb2oxTzd1bXNuVFpzVDFZeTBNeWhqUXZwMFN1ekhYMGJlcXk4Ny1Kd0xNVjdfM08wRkV6RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>682efa9e1e934abcbfc26cf64682625c</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>85b1ba799ab341a48dcf815b</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>f94f68e6c30c6b9ec890c074</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr"/>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr"/>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL4"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
